--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-wai-physical-demands-answer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
